--- a/docs/import-examples/06 Workers.xlsx
+++ b/docs/import-examples/06 Workers.xlsx
@@ -590,7 +590,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:I505"/>
+  <dimension ref="A1:I300"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="22" customWidth="1"/>
@@ -632,11 +632,151 @@
         <v>8</v>
       </c>
     </row>
-    <row r="2" spans="4:4" x14ac:dyDescent="0.25"/>
-    <row r="3" spans="4:4" x14ac:dyDescent="0.25"/>
-    <row r="4" spans="4:4" x14ac:dyDescent="0.25"/>
-    <row r="5" spans="4:4" x14ac:dyDescent="0.25"/>
-    <row r="6" spans="4:4" x14ac:dyDescent="0.25"/>
+    <row r="2" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A2" t="s">
+        <v>9</v>
+      </c>
+      <c r="B2" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="C2" t="s">
+        <v>11</v>
+      </c>
+      <c r="D2" t="s">
+        <v>12</v>
+      </c>
+      <c r="E2">
+        <v>0</v>
+      </c>
+      <c r="F2">
+        <v>0</v>
+      </c>
+      <c r="G2">
+        <v>25000</v>
+      </c>
+      <c r="H2" t="s">
+        <v>13</v>
+      </c>
+      <c r="I2" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="3" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A3" t="s">
+        <v>15</v>
+      </c>
+      <c r="B3" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="C3" t="s">
+        <v>17</v>
+      </c>
+      <c r="D3" t="s">
+        <v>18</v>
+      </c>
+      <c r="E3">
+        <v>900</v>
+      </c>
+      <c r="F3">
+        <v>1300</v>
+      </c>
+      <c r="G3">
+        <v>0</v>
+      </c>
+      <c r="H3" t="s">
+        <v>19</v>
+      </c>
+      <c r="I3" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="4" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A4" t="s">
+        <v>21</v>
+      </c>
+      <c r="B4" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="C4" t="s">
+        <v>23</v>
+      </c>
+      <c r="D4" t="s">
+        <v>18</v>
+      </c>
+      <c r="E4">
+        <v>600</v>
+      </c>
+      <c r="F4">
+        <v>900</v>
+      </c>
+      <c r="G4">
+        <v>0</v>
+      </c>
+      <c r="H4" t="s">
+        <v>24</v>
+      </c>
+      <c r="I4" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="5" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A5" t="s">
+        <v>26</v>
+      </c>
+      <c r="B5" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="C5" t="s">
+        <v>28</v>
+      </c>
+      <c r="D5" t="s">
+        <v>18</v>
+      </c>
+      <c r="E5">
+        <v>500</v>
+      </c>
+      <c r="F5">
+        <v>800</v>
+      </c>
+      <c r="G5">
+        <v>0</v>
+      </c>
+      <c r="H5" t="s">
+        <v>29</v>
+      </c>
+      <c r="I5" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="6" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A6" t="s">
+        <v>31</v>
+      </c>
+      <c r="B6" s="3" t="s">
+        <v>32</v>
+      </c>
+      <c r="C6" t="s">
+        <v>33</v>
+      </c>
+      <c r="D6" t="s">
+        <v>12</v>
+      </c>
+      <c r="E6">
+        <v>0</v>
+      </c>
+      <c r="F6">
+        <v>0</v>
+      </c>
+      <c r="G6">
+        <v>18000</v>
+      </c>
+      <c r="H6" t="s">
+        <v>34</v>
+      </c>
+      <c r="I6" t="s">
+        <v>35</v>
+      </c>
+    </row>
     <row r="7" spans="4:4" x14ac:dyDescent="0.25"/>
     <row r="8" spans="4:4" x14ac:dyDescent="0.25"/>
     <row r="9" spans="4:4" x14ac:dyDescent="0.25"/>
@@ -931,357 +1071,12 @@
     <row r="298" spans="4:4" x14ac:dyDescent="0.25"/>
     <row r="299" spans="4:4" x14ac:dyDescent="0.25"/>
     <row r="300" spans="4:4" x14ac:dyDescent="0.25"/>
-    <row r="301" spans="4:4" x14ac:dyDescent="0.25"/>
-    <row r="302" spans="4:4" x14ac:dyDescent="0.25"/>
-    <row r="303" spans="4:4" x14ac:dyDescent="0.25"/>
-    <row r="304" spans="4:4" x14ac:dyDescent="0.25"/>
-    <row r="305" spans="4:4" x14ac:dyDescent="0.25"/>
-    <row r="306" spans="4:4" x14ac:dyDescent="0.25"/>
-    <row r="307" spans="4:4" x14ac:dyDescent="0.25"/>
-    <row r="308" spans="4:4" x14ac:dyDescent="0.25"/>
-    <row r="309" spans="4:4" x14ac:dyDescent="0.25"/>
-    <row r="310" spans="4:4" x14ac:dyDescent="0.25"/>
-    <row r="311" spans="4:4" x14ac:dyDescent="0.25"/>
-    <row r="312" spans="4:4" x14ac:dyDescent="0.25"/>
-    <row r="313" spans="4:4" x14ac:dyDescent="0.25"/>
-    <row r="314" spans="4:4" x14ac:dyDescent="0.25"/>
-    <row r="315" spans="4:4" x14ac:dyDescent="0.25"/>
-    <row r="316" spans="4:4" x14ac:dyDescent="0.25"/>
-    <row r="317" spans="4:4" x14ac:dyDescent="0.25"/>
-    <row r="318" spans="4:4" x14ac:dyDescent="0.25"/>
-    <row r="319" spans="4:4" x14ac:dyDescent="0.25"/>
-    <row r="320" spans="4:4" x14ac:dyDescent="0.25"/>
-    <row r="321" spans="4:4" x14ac:dyDescent="0.25"/>
-    <row r="322" spans="4:4" x14ac:dyDescent="0.25"/>
-    <row r="323" spans="4:4" x14ac:dyDescent="0.25"/>
-    <row r="324" spans="4:4" x14ac:dyDescent="0.25"/>
-    <row r="325" spans="4:4" x14ac:dyDescent="0.25"/>
-    <row r="326" spans="4:4" x14ac:dyDescent="0.25"/>
-    <row r="327" spans="4:4" x14ac:dyDescent="0.25"/>
-    <row r="328" spans="4:4" x14ac:dyDescent="0.25"/>
-    <row r="329" spans="4:4" x14ac:dyDescent="0.25"/>
-    <row r="330" spans="4:4" x14ac:dyDescent="0.25"/>
-    <row r="331" spans="4:4" x14ac:dyDescent="0.25"/>
-    <row r="332" spans="4:4" x14ac:dyDescent="0.25"/>
-    <row r="333" spans="4:4" x14ac:dyDescent="0.25"/>
-    <row r="334" spans="4:4" x14ac:dyDescent="0.25"/>
-    <row r="335" spans="4:4" x14ac:dyDescent="0.25"/>
-    <row r="336" spans="4:4" x14ac:dyDescent="0.25"/>
-    <row r="337" spans="4:4" x14ac:dyDescent="0.25"/>
-    <row r="338" spans="4:4" x14ac:dyDescent="0.25"/>
-    <row r="339" spans="4:4" x14ac:dyDescent="0.25"/>
-    <row r="340" spans="4:4" x14ac:dyDescent="0.25"/>
-    <row r="341" spans="4:4" x14ac:dyDescent="0.25"/>
-    <row r="342" spans="4:4" x14ac:dyDescent="0.25"/>
-    <row r="343" spans="4:4" x14ac:dyDescent="0.25"/>
-    <row r="344" spans="4:4" x14ac:dyDescent="0.25"/>
-    <row r="345" spans="4:4" x14ac:dyDescent="0.25"/>
-    <row r="346" spans="4:4" x14ac:dyDescent="0.25"/>
-    <row r="347" spans="4:4" x14ac:dyDescent="0.25"/>
-    <row r="348" spans="4:4" x14ac:dyDescent="0.25"/>
-    <row r="349" spans="4:4" x14ac:dyDescent="0.25"/>
-    <row r="350" spans="4:4" x14ac:dyDescent="0.25"/>
-    <row r="351" spans="4:4" x14ac:dyDescent="0.25"/>
-    <row r="352" spans="4:4" x14ac:dyDescent="0.25"/>
-    <row r="353" spans="4:4" x14ac:dyDescent="0.25"/>
-    <row r="354" spans="4:4" x14ac:dyDescent="0.25"/>
-    <row r="355" spans="4:4" x14ac:dyDescent="0.25"/>
-    <row r="356" spans="4:4" x14ac:dyDescent="0.25"/>
-    <row r="357" spans="4:4" x14ac:dyDescent="0.25"/>
-    <row r="358" spans="4:4" x14ac:dyDescent="0.25"/>
-    <row r="359" spans="4:4" x14ac:dyDescent="0.25"/>
-    <row r="360" spans="4:4" x14ac:dyDescent="0.25"/>
-    <row r="361" spans="4:4" x14ac:dyDescent="0.25"/>
-    <row r="362" spans="4:4" x14ac:dyDescent="0.25"/>
-    <row r="363" spans="4:4" x14ac:dyDescent="0.25"/>
-    <row r="364" spans="4:4" x14ac:dyDescent="0.25"/>
-    <row r="365" spans="4:4" x14ac:dyDescent="0.25"/>
-    <row r="366" spans="4:4" x14ac:dyDescent="0.25"/>
-    <row r="367" spans="4:4" x14ac:dyDescent="0.25"/>
-    <row r="368" spans="4:4" x14ac:dyDescent="0.25"/>
-    <row r="369" spans="4:4" x14ac:dyDescent="0.25"/>
-    <row r="370" spans="4:4" x14ac:dyDescent="0.25"/>
-    <row r="371" spans="4:4" x14ac:dyDescent="0.25"/>
-    <row r="372" spans="4:4" x14ac:dyDescent="0.25"/>
-    <row r="373" spans="4:4" x14ac:dyDescent="0.25"/>
-    <row r="374" spans="4:4" x14ac:dyDescent="0.25"/>
-    <row r="375" spans="4:4" x14ac:dyDescent="0.25"/>
-    <row r="376" spans="4:4" x14ac:dyDescent="0.25"/>
-    <row r="377" spans="4:4" x14ac:dyDescent="0.25"/>
-    <row r="378" spans="4:4" x14ac:dyDescent="0.25"/>
-    <row r="379" spans="4:4" x14ac:dyDescent="0.25"/>
-    <row r="380" spans="4:4" x14ac:dyDescent="0.25"/>
-    <row r="381" spans="4:4" x14ac:dyDescent="0.25"/>
-    <row r="382" spans="4:4" x14ac:dyDescent="0.25"/>
-    <row r="383" spans="4:4" x14ac:dyDescent="0.25"/>
-    <row r="384" spans="4:4" x14ac:dyDescent="0.25"/>
-    <row r="385" spans="4:4" x14ac:dyDescent="0.25"/>
-    <row r="386" spans="4:4" x14ac:dyDescent="0.25"/>
-    <row r="387" spans="4:4" x14ac:dyDescent="0.25"/>
-    <row r="388" spans="4:4" x14ac:dyDescent="0.25"/>
-    <row r="389" spans="4:4" x14ac:dyDescent="0.25"/>
-    <row r="390" spans="4:4" x14ac:dyDescent="0.25"/>
-    <row r="391" spans="4:4" x14ac:dyDescent="0.25"/>
-    <row r="392" spans="4:4" x14ac:dyDescent="0.25"/>
-    <row r="393" spans="4:4" x14ac:dyDescent="0.25"/>
-    <row r="394" spans="4:4" x14ac:dyDescent="0.25"/>
-    <row r="395" spans="4:4" x14ac:dyDescent="0.25"/>
-    <row r="396" spans="4:4" x14ac:dyDescent="0.25"/>
-    <row r="397" spans="4:4" x14ac:dyDescent="0.25"/>
-    <row r="398" spans="4:4" x14ac:dyDescent="0.25"/>
-    <row r="399" spans="4:4" x14ac:dyDescent="0.25"/>
-    <row r="400" spans="4:4" x14ac:dyDescent="0.25"/>
-    <row r="401" spans="4:4" x14ac:dyDescent="0.25"/>
-    <row r="402" spans="4:4" x14ac:dyDescent="0.25"/>
-    <row r="403" spans="4:4" x14ac:dyDescent="0.25"/>
-    <row r="404" spans="4:4" x14ac:dyDescent="0.25"/>
-    <row r="405" spans="4:4" x14ac:dyDescent="0.25"/>
-    <row r="406" spans="4:4" x14ac:dyDescent="0.25"/>
-    <row r="407" spans="4:4" x14ac:dyDescent="0.25"/>
-    <row r="408" spans="4:4" x14ac:dyDescent="0.25"/>
-    <row r="409" spans="4:4" x14ac:dyDescent="0.25"/>
-    <row r="410" spans="4:4" x14ac:dyDescent="0.25"/>
-    <row r="411" spans="4:4" x14ac:dyDescent="0.25"/>
-    <row r="412" spans="4:4" x14ac:dyDescent="0.25"/>
-    <row r="413" spans="4:4" x14ac:dyDescent="0.25"/>
-    <row r="414" spans="4:4" x14ac:dyDescent="0.25"/>
-    <row r="415" spans="4:4" x14ac:dyDescent="0.25"/>
-    <row r="416" spans="4:4" x14ac:dyDescent="0.25"/>
-    <row r="417" spans="4:4" x14ac:dyDescent="0.25"/>
-    <row r="418" spans="4:4" x14ac:dyDescent="0.25"/>
-    <row r="419" spans="4:4" x14ac:dyDescent="0.25"/>
-    <row r="420" spans="4:4" x14ac:dyDescent="0.25"/>
-    <row r="421" spans="4:4" x14ac:dyDescent="0.25"/>
-    <row r="422" spans="4:4" x14ac:dyDescent="0.25"/>
-    <row r="423" spans="4:4" x14ac:dyDescent="0.25"/>
-    <row r="424" spans="4:4" x14ac:dyDescent="0.25"/>
-    <row r="425" spans="4:4" x14ac:dyDescent="0.25"/>
-    <row r="426" spans="4:4" x14ac:dyDescent="0.25"/>
-    <row r="427" spans="4:4" x14ac:dyDescent="0.25"/>
-    <row r="428" spans="4:4" x14ac:dyDescent="0.25"/>
-    <row r="429" spans="4:4" x14ac:dyDescent="0.25"/>
-    <row r="430" spans="4:4" x14ac:dyDescent="0.25"/>
-    <row r="431" spans="4:4" x14ac:dyDescent="0.25"/>
-    <row r="432" spans="4:4" x14ac:dyDescent="0.25"/>
-    <row r="433" spans="4:4" x14ac:dyDescent="0.25"/>
-    <row r="434" spans="4:4" x14ac:dyDescent="0.25"/>
-    <row r="435" spans="4:4" x14ac:dyDescent="0.25"/>
-    <row r="436" spans="4:4" x14ac:dyDescent="0.25"/>
-    <row r="437" spans="4:4" x14ac:dyDescent="0.25"/>
-    <row r="438" spans="4:4" x14ac:dyDescent="0.25"/>
-    <row r="439" spans="4:4" x14ac:dyDescent="0.25"/>
-    <row r="440" spans="4:4" x14ac:dyDescent="0.25"/>
-    <row r="441" spans="4:4" x14ac:dyDescent="0.25"/>
-    <row r="442" spans="4:4" x14ac:dyDescent="0.25"/>
-    <row r="443" spans="4:4" x14ac:dyDescent="0.25"/>
-    <row r="444" spans="4:4" x14ac:dyDescent="0.25"/>
-    <row r="445" spans="4:4" x14ac:dyDescent="0.25"/>
-    <row r="446" spans="4:4" x14ac:dyDescent="0.25"/>
-    <row r="447" spans="4:4" x14ac:dyDescent="0.25"/>
-    <row r="448" spans="4:4" x14ac:dyDescent="0.25"/>
-    <row r="449" spans="4:4" x14ac:dyDescent="0.25"/>
-    <row r="450" spans="4:4" x14ac:dyDescent="0.25"/>
-    <row r="451" spans="4:4" x14ac:dyDescent="0.25"/>
-    <row r="452" spans="4:4" x14ac:dyDescent="0.25"/>
-    <row r="453" spans="4:4" x14ac:dyDescent="0.25"/>
-    <row r="454" spans="4:4" x14ac:dyDescent="0.25"/>
-    <row r="455" spans="4:4" x14ac:dyDescent="0.25"/>
-    <row r="456" spans="4:4" x14ac:dyDescent="0.25"/>
-    <row r="457" spans="4:4" x14ac:dyDescent="0.25"/>
-    <row r="458" spans="4:4" x14ac:dyDescent="0.25"/>
-    <row r="459" spans="4:4" x14ac:dyDescent="0.25"/>
-    <row r="460" spans="4:4" x14ac:dyDescent="0.25"/>
-    <row r="461" spans="4:4" x14ac:dyDescent="0.25"/>
-    <row r="462" spans="4:4" x14ac:dyDescent="0.25"/>
-    <row r="463" spans="4:4" x14ac:dyDescent="0.25"/>
-    <row r="464" spans="4:4" x14ac:dyDescent="0.25"/>
-    <row r="465" spans="4:4" x14ac:dyDescent="0.25"/>
-    <row r="466" spans="4:4" x14ac:dyDescent="0.25"/>
-    <row r="467" spans="4:4" x14ac:dyDescent="0.25"/>
-    <row r="468" spans="4:4" x14ac:dyDescent="0.25"/>
-    <row r="469" spans="4:4" x14ac:dyDescent="0.25"/>
-    <row r="470" spans="4:4" x14ac:dyDescent="0.25"/>
-    <row r="471" spans="4:4" x14ac:dyDescent="0.25"/>
-    <row r="472" spans="4:4" x14ac:dyDescent="0.25"/>
-    <row r="473" spans="4:4" x14ac:dyDescent="0.25"/>
-    <row r="474" spans="4:4" x14ac:dyDescent="0.25"/>
-    <row r="475" spans="4:4" x14ac:dyDescent="0.25"/>
-    <row r="476" spans="4:4" x14ac:dyDescent="0.25"/>
-    <row r="477" spans="4:4" x14ac:dyDescent="0.25"/>
-    <row r="478" spans="4:4" x14ac:dyDescent="0.25"/>
-    <row r="479" spans="4:4" x14ac:dyDescent="0.25"/>
-    <row r="480" spans="4:4" x14ac:dyDescent="0.25"/>
-    <row r="481" spans="4:4" x14ac:dyDescent="0.25"/>
-    <row r="482" spans="4:4" x14ac:dyDescent="0.25"/>
-    <row r="483" spans="4:4" x14ac:dyDescent="0.25"/>
-    <row r="484" spans="4:4" x14ac:dyDescent="0.25"/>
-    <row r="485" spans="4:4" x14ac:dyDescent="0.25"/>
-    <row r="486" spans="4:4" x14ac:dyDescent="0.25"/>
-    <row r="487" spans="4:4" x14ac:dyDescent="0.25"/>
-    <row r="488" spans="4:4" x14ac:dyDescent="0.25"/>
-    <row r="489" spans="4:4" x14ac:dyDescent="0.25"/>
-    <row r="490" spans="4:4" x14ac:dyDescent="0.25"/>
-    <row r="491" spans="4:4" x14ac:dyDescent="0.25"/>
-    <row r="492" spans="4:4" x14ac:dyDescent="0.25"/>
-    <row r="493" spans="4:4" x14ac:dyDescent="0.25"/>
-    <row r="494" spans="4:4" x14ac:dyDescent="0.25"/>
-    <row r="495" spans="4:4" x14ac:dyDescent="0.25"/>
-    <row r="496" spans="4:4" x14ac:dyDescent="0.25"/>
-    <row r="497" spans="4:4" x14ac:dyDescent="0.25"/>
-    <row r="498" spans="4:4" x14ac:dyDescent="0.25"/>
-    <row r="499" spans="4:4" x14ac:dyDescent="0.25"/>
-    <row r="500" spans="4:4" x14ac:dyDescent="0.25"/>
-    <row r="501" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A501" t="s">
-        <v>9</v>
-      </c>
-      <c r="B501" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="C501" t="s">
-        <v>11</v>
-      </c>
-      <c r="D501" t="s">
-        <v>12</v>
-      </c>
-      <c r="E501">
-        <v>0</v>
-      </c>
-      <c r="F501">
-        <v>0</v>
-      </c>
-      <c r="G501">
-        <v>25000</v>
-      </c>
-      <c r="H501" t="s">
-        <v>13</v>
-      </c>
-      <c r="I501" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="502" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A502" t="s">
-        <v>15</v>
-      </c>
-      <c r="B502" s="3" t="s">
-        <v>16</v>
-      </c>
-      <c r="C502" t="s">
-        <v>17</v>
-      </c>
-      <c r="D502" t="s">
-        <v>18</v>
-      </c>
-      <c r="E502">
-        <v>900</v>
-      </c>
-      <c r="F502">
-        <v>1300</v>
-      </c>
-      <c r="G502">
-        <v>0</v>
-      </c>
-      <c r="H502" t="s">
-        <v>19</v>
-      </c>
-      <c r="I502" t="s">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="503" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A503" t="s">
-        <v>21</v>
-      </c>
-      <c r="B503" s="3" t="s">
-        <v>22</v>
-      </c>
-      <c r="C503" t="s">
-        <v>23</v>
-      </c>
-      <c r="D503" t="s">
-        <v>18</v>
-      </c>
-      <c r="E503">
-        <v>600</v>
-      </c>
-      <c r="F503">
-        <v>900</v>
-      </c>
-      <c r="G503">
-        <v>0</v>
-      </c>
-      <c r="H503" t="s">
-        <v>24</v>
-      </c>
-      <c r="I503" t="s">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="504" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A504" t="s">
-        <v>26</v>
-      </c>
-      <c r="B504" s="3" t="s">
-        <v>27</v>
-      </c>
-      <c r="C504" t="s">
-        <v>28</v>
-      </c>
-      <c r="D504" t="s">
-        <v>18</v>
-      </c>
-      <c r="E504">
-        <v>500</v>
-      </c>
-      <c r="F504">
-        <v>800</v>
-      </c>
-      <c r="G504">
-        <v>0</v>
-      </c>
-      <c r="H504" t="s">
-        <v>29</v>
-      </c>
-      <c r="I504" t="s">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="505" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A505" t="s">
-        <v>31</v>
-      </c>
-      <c r="B505" s="3" t="s">
-        <v>32</v>
-      </c>
-      <c r="C505" t="s">
-        <v>33</v>
-      </c>
-      <c r="D505" t="s">
-        <v>12</v>
-      </c>
-      <c r="E505">
-        <v>0</v>
-      </c>
-      <c r="F505">
-        <v>0</v>
-      </c>
-      <c r="G505">
-        <v>18000</v>
-      </c>
-      <c r="H505" t="s">
-        <v>34</v>
-      </c>
-      <c r="I505" t="s">
-        <v>35</v>
-      </c>
-    </row>
   </sheetData>
   <dataValidations count="2">
-    <dataValidation type="list" allowBlank="1" showErrorMessage="1" errorTitle="Type" error="Choose one of: Salaried, Daily wage, Contractor" sqref="D10:D500">
+    <dataValidation type="list" allowBlank="1" showErrorMessage="1" errorTitle="Type" error="Choose one of: Salaried, Daily wage, Contractor" sqref="D10:D300">
       <formula1>"Salaried,Daily wage,Contractor"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showErrorMessage="1" errorTitle="Type" error="Choose one of: Salaried, Daily wage, Contractor" sqref="D2:D500">
+    <dataValidation type="list" allowBlank="1" showErrorMessage="1" errorTitle="Type" error="Choose one of: Salaried, Daily wage, Contractor" sqref="D2:D300">
       <formula1>"Salaried,Daily wage,Contractor"</formula1>
     </dataValidation>
   </dataValidations>
